--- a/docs/documents/mt1/Groepsopdracht1.xlsx
+++ b/docs/documents/mt1/Groepsopdracht1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vink0109/Library/Mobile Documents/com~apple~CloudDocs/dev/mod12/documents/mt1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AB81121-99CB-C847-A3B7-F892D11531FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DC70EB-05DE-FA4B-8A27-6323702C260B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20380" yWindow="5480" windowWidth="28040" windowHeight="17180" xr2:uid="{B6B3CA91-1A7C-A341-9164-5621859DA94B}"/>
+    <workbookView xWindow="5180" yWindow="2300" windowWidth="28040" windowHeight="17180" xr2:uid="{B6B3CA91-1A7C-A341-9164-5621859DA94B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -233,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -243,14 +243,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,7 +588,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="56.33203125" customWidth="1"/>
-    <col min="3" max="3" width="94.33203125" customWidth="1"/>
+    <col min="3" max="3" width="57.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="22" x14ac:dyDescent="0.25">
@@ -655,46 +654,46 @@
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B15" s="7"/>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B16" s="7"/>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B17" s="7"/>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -702,7 +701,7 @@
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="2:3" ht="22" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
@@ -711,7 +710,7 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="2:3" ht="22" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="2"/>
@@ -744,7 +743,7 @@
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
